--- a/ig/DM-37/CodeSystem-TRE-R260-HL7RoleClass.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R260-HL7RoleClass.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -169,7 +169,7 @@
     <t>ECON</t>
   </si>
   <si>
-    <t>Entité à contacter en cas d'urgence</t>
+    <t>personne à prévenir en cas d'urgence</t>
   </si>
   <si>
     <t>GUARD</t>
@@ -205,7 +205,7 @@
     <t>PAT</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>aidé</t>
   </si>
   <si>
     <t>PROV</t>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>Professionnel caractérisé par son rôle</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>personne de confiance</t>
   </si>
 </sst>
 </file>
@@ -591,7 +597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -716,6 +722,18 @@
       </c>
       <c r="D10" s="2"/>
     </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
